--- a/output/lgbm_reg/03_model_tuning/tuning_log.xlsx
+++ b/output/lgbm_reg/03_model_tuning/tuning_log.xlsx
@@ -557,19 +557,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1.292648</v>
+        <v>1.020964</v>
       </c>
       <c r="D2" t="b">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3104</v>
+        <v>0.3623</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5162</v>
+        <v>0.4221</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4891</v>
+        <v>0.4274</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         <v>5</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="V2" t="n">
         <v>800</v>
@@ -633,19 +633,19 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>1.209097</v>
+        <v>0.975789</v>
       </c>
       <c r="D3" t="b">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5967</v>
+        <v>0.3824</v>
       </c>
       <c r="F3" t="n">
-        <v>0.708</v>
+        <v>0.4179</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6429</v>
+        <v>0.4217</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -678,25 +678,25 @@
         <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>0.008594045111996377</v>
+        <v>0.03286254062746905</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="T3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V3" t="n">
-        <v>700</v>
+        <v>950</v>
       </c>
     </row>
     <row r="4">
@@ -709,19 +709,19 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>1.502953</v>
+        <v>1.058793</v>
       </c>
       <c r="D4" t="b">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2522</v>
+        <v>0.3474</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5449000000000001</v>
+        <v>0.4126</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4947</v>
+        <v>0.4291</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -748,107 +748,107 @@
         <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>104</v>
+        <v>24</v>
       </c>
       <c r="O4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>0.04299719431008326</v>
+        <v>0.02347382422783625</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>6</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V4" t="n">
-        <v>650</v>
+        <v>550</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>第2轮</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>1.162025</v>
-      </c>
-      <c r="D5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0.4891</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.657</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0.5506</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="C5" t="n">
+        <v>1.030612</v>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4218</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4262</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>gbdt</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>regression</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>mae</t>
         </is>
       </c>
-      <c r="K5" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="O5" s="2" t="n">
+      <c r="K5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>32</v>
+      </c>
+      <c r="O5" t="n">
         <v>7</v>
       </c>
-      <c r="P5" s="2" t="n">
-        <v>0.04277450915108289</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>0.7000000000000001</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>950</v>
+      <c r="P5" t="n">
+        <v>0.03631378747815298</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>20</v>
+      </c>
+      <c r="V5" t="n">
+        <v>650</v>
       </c>
     </row>
     <row r="6">
@@ -861,19 +861,19 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>1.163198</v>
+        <v>1.01423</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4355</v>
+        <v>0.3676</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5935</v>
+        <v>0.4199</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5255</v>
+        <v>0.4275</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -900,31 +900,31 @@
         <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="O6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03037573951868842</v>
+        <v>0.04734587653345524</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V6" t="n">
-        <v>800</v>
+        <v>850</v>
       </c>
     </row>
     <row r="7">
@@ -937,19 +937,19 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>1.218729</v>
+        <v>0.985613</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5118</v>
+        <v>0.3779</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6526</v>
+        <v>0.4211</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6055</v>
+        <v>0.4235</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -982,25 +982,25 @@
         <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0123226943928357</v>
+        <v>0.0277947212036319</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6000000000000001</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V7" t="n">
-        <v>650</v>
+        <v>900</v>
       </c>
     </row>
     <row r="8">
@@ -1013,19 +1013,19 @@
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>1.186806</v>
+        <v>0.985027</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5542</v>
+        <v>0.3776</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6802</v>
+        <v>0.4149</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6069</v>
+        <v>0.4217</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1052,28 +1052,28 @@
         <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="O8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01397621027718759</v>
+        <v>0.03773708771083101</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="R8" t="n">
         <v>0.8</v>
       </c>
       <c r="S8" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V8" t="n">
         <v>700</v>
@@ -1089,19 +1089,19 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>1.164592</v>
+        <v>1.058093</v>
       </c>
       <c r="D9" t="b">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.416</v>
+        <v>0.354</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5736</v>
+        <v>0.4276</v>
       </c>
       <c r="G9" t="n">
-        <v>0.515</v>
+        <v>0.4361</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1128,31 +1128,31 @@
         <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="O9" t="n">
         <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>0.02066498925114593</v>
+        <v>0.01399366354020606</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V9" t="n">
-        <v>950</v>
+        <v>700</v>
       </c>
     </row>
     <row r="10">
@@ -1165,19 +1165,19 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>1.226564</v>
+        <v>0.960224</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3715</v>
+        <v>0.4099</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5666</v>
+        <v>0.4211</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5101</v>
+        <v>0.4298</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1204,31 +1204,31 @@
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01053301934447673</v>
+        <v>0.02653886513063454</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="T10" t="n">
         <v>19</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="V10" t="n">
-        <v>700</v>
+        <v>750</v>
       </c>
     </row>
     <row r="11">
@@ -1241,19 +1241,19 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>1.252305</v>
+        <v>0.95802</v>
       </c>
       <c r="D11" t="b">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3355</v>
+        <v>0.4038</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5256999999999999</v>
+        <v>0.4193</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4961</v>
+        <v>0.4259</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1280,31 +1280,31 @@
         <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="O11" t="n">
         <v>8</v>
       </c>
       <c r="P11" t="n">
-        <v>0.03514381443894363</v>
+        <v>0.01610398044226858</v>
       </c>
       <c r="Q11" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="R11" t="n">
         <v>0.7000000000000001</v>
       </c>
-      <c r="R11" t="n">
-        <v>0.8</v>
-      </c>
       <c r="S11" t="n">
+        <v>13</v>
+      </c>
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" t="n">
-        <v>10</v>
-      </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V11" t="n">
-        <v>750</v>
+        <v>650</v>
       </c>
     </row>
     <row r="12">
@@ -1317,19 +1317,19 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>1.166505</v>
+        <v>0.9931410000000001</v>
       </c>
       <c r="D12" t="b">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4416</v>
+        <v>0.375</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5995</v>
+        <v>0.4216</v>
       </c>
       <c r="G12" t="n">
-        <v>0.531</v>
+        <v>0.4247</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1356,31 +1356,31 @@
         <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0318882190794512</v>
+        <v>0.03442838781425329</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
         <v>14</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V12" t="n">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="13">
@@ -1393,19 +1393,19 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>1.341069</v>
+        <v>1.072569</v>
       </c>
       <c r="D13" t="b">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3029</v>
+        <v>0.3374</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5099</v>
+        <v>0.4225</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5048</v>
+        <v>0.43</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1432,31 +1432,31 @@
         <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="O13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P13" t="n">
-        <v>0.01273664833308307</v>
+        <v>0.04245609029096042</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V13" t="n">
-        <v>950</v>
+        <v>750</v>
       </c>
     </row>
     <row r="14">
@@ -1469,19 +1469,19 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>1.276364</v>
+        <v>0.979768</v>
       </c>
       <c r="D14" t="b">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3379</v>
+        <v>0.3806</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5812</v>
+        <v>0.4181</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4972</v>
+        <v>0.4222</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1508,31 +1508,31 @@
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="O14" t="n">
         <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>0.02877350521974565</v>
+        <v>0.03500788670523837</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V14" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="15">
@@ -1545,19 +1545,19 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>1.177003</v>
+        <v>0.968659</v>
       </c>
       <c r="D15" t="b">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3954</v>
+        <v>0.3922</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5666</v>
+        <v>0.4202</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.4245</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1584,107 +1584,107 @@
         <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="O15" t="n">
         <v>6</v>
       </c>
       <c r="P15" t="n">
-        <v>0.04957548874545592</v>
+        <v>0.01467922918340945</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="R15" t="n">
         <v>0.8</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T15" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V15" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>第2轮</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="C16" t="n">
-        <v>1.862151</v>
-      </c>
-      <c r="D16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.1874</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.5483</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.5004</v>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="C16" s="2" t="n">
+        <v>0.9573199999999999</v>
+      </c>
+      <c r="D16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0.3937</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0.4197</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>0.4213</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>gbdt</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>regression</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>mae</t>
         </is>
       </c>
-      <c r="K16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>2</v>
-      </c>
-      <c r="N16" t="n">
-        <v>96</v>
-      </c>
-      <c r="O16" t="n">
-        <v>8</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.03491177048840533</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="K16" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>0.03717046832225854</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="R16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>8</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>650</v>
+      <c r="S16" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>550</v>
       </c>
     </row>
     <row r="17">
@@ -1697,19 +1697,19 @@
         <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>1.351019</v>
+        <v>0.963243</v>
       </c>
       <c r="D17" t="b">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3015</v>
+        <v>0.4029</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5626</v>
+        <v>0.4219</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4946</v>
+        <v>0.4279</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1736,31 +1736,31 @@
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="O17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>0.02516277730156447</v>
+        <v>0.01877987942161911</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="V17" t="n">
-        <v>850</v>
+        <v>800</v>
       </c>
     </row>
     <row r="18">
@@ -1773,19 +1773,19 @@
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>1.953717</v>
+        <v>1.016334</v>
       </c>
       <c r="D18" t="b">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1762</v>
+        <v>0.3697</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5029</v>
+        <v>0.4196</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5082</v>
+        <v>0.4291</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1812,31 +1812,31 @@
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="O18" t="n">
         <v>6</v>
       </c>
       <c r="P18" t="n">
-        <v>0.04999348076610432</v>
+        <v>0.0140233570176525</v>
       </c>
       <c r="Q18" t="n">
         <v>0.9</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V18" t="n">
-        <v>850</v>
+        <v>750</v>
       </c>
     </row>
     <row r="19">
@@ -1849,19 +1849,19 @@
         <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>1.561503</v>
+        <v>0.97209</v>
       </c>
       <c r="D19" t="b">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2368</v>
+        <v>0.3914</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5074</v>
+        <v>0.4187</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.4249</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1888,31 +1888,31 @@
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="O19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P19" t="n">
-        <v>0.02842258208642139</v>
+        <v>0.03228974427411316</v>
       </c>
       <c r="Q19" t="n">
         <v>0.8</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V19" t="n">
-        <v>650</v>
+        <v>750</v>
       </c>
     </row>
     <row r="20">
@@ -1925,19 +1925,19 @@
         <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>1.314942</v>
+        <v>0.978181</v>
       </c>
       <c r="D20" t="b">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3037</v>
+        <v>0.4282</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5139</v>
+        <v>0.4438</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4921</v>
+        <v>0.4495</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1964,31 +1964,31 @@
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="O20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P20" t="n">
-        <v>0.03456304023662498</v>
+        <v>0.008269152169428261</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.9</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V20" t="n">
-        <v>850</v>
+        <v>550</v>
       </c>
     </row>
     <row r="21">
@@ -2001,19 +2001,19 @@
         <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>1.678158</v>
+        <v>0.975458</v>
       </c>
       <c r="D21" t="b">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2153</v>
+        <v>0.3857</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4951</v>
+        <v>0.4187</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5036</v>
+        <v>0.4233</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2040,31 +2040,31 @@
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="O21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>0.04182562713339056</v>
+        <v>0.04578975340313516</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V21" t="n">
-        <v>950</v>
+        <v>550</v>
       </c>
     </row>
     <row r="22">
@@ -2077,19 +2077,19 @@
         <v>20</v>
       </c>
       <c r="C22" t="n">
-        <v>2.022107</v>
+        <v>0.9660069999999999</v>
       </c>
       <c r="D22" t="b">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1762</v>
+        <v>0.3993</v>
       </c>
       <c r="F22" t="n">
-        <v>0.534</v>
+        <v>0.4235</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5256999999999999</v>
+        <v>0.4276</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2116,31 +2116,31 @@
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="O22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P22" t="n">
-        <v>0.01038365525799906</v>
+        <v>0.04865167075419103</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="R22" t="n">
         <v>0.7000000000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T22" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="V22" t="n">
-        <v>650</v>
+        <v>750</v>
       </c>
     </row>
   </sheetData>
